--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123576440</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,238 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123787951</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57503</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Jonsatorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>337931</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6426938</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123787899</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57503</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hällebäckahult, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>337848</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6427040</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123576440</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>123787951</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>123787899</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123576440</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123787951</v>
+        <v>123787899</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jonsatorp, Vg</t>
+          <t>Hällebäckahult, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337931</v>
+        <v>337848</v>
       </c>
       <c r="R3" t="n">
-        <v>6426938</v>
+        <v>6427040</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123787899</v>
+        <v>123787951</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,14 +942,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällebäckahult, Vg</t>
+          <t>Jonsatorp, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337848</v>
+        <v>337931</v>
       </c>
       <c r="R4" t="n">
-        <v>6427040</v>
+        <v>6426938</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,6 +1016,233 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123577092</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hällebäckahult, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>337869</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6427098</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124766669</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57664</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hällebäckahult, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>337924</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6426985</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123577092</v>
+        <v>124766654</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57664</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R5" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,17 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124766669</v>
+        <v>123577092</v>
       </c>
       <c r="B6" t="n">
-        <v>57664</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,16 +1150,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337924</v>
+        <v>337869</v>
       </c>
       <c r="R6" t="n">
-        <v>6426985</v>
+        <v>6427098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,22 +1208,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124766654</v>
+        <v>123577092</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337924</v>
+        <v>337869</v>
       </c>
       <c r="R5" t="n">
-        <v>6426985</v>
+        <v>6427098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,22 +1092,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123577092</v>
+        <v>124766654</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57664</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,16 +1145,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R6" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,17 +1203,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1129,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124766654</v>
+        <v>124766669</v>
       </c>
       <c r="B6" t="n">
         <v>57664</v>

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123577092</v>
+        <v>124766669</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57664</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R5" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,17 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124766669</v>
+        <v>123577092</v>
       </c>
       <c r="B6" t="n">
-        <v>57664</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,16 +1150,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337924</v>
+        <v>337869</v>
       </c>
       <c r="R6" t="n">
-        <v>6426985</v>
+        <v>6427098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,22 +1208,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124766669</v>
+        <v>123577092</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337924</v>
+        <v>337869</v>
       </c>
       <c r="R5" t="n">
-        <v>6426985</v>
+        <v>6427098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,22 +1092,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123577092</v>
+        <v>124766669</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57664</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,16 +1145,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R6" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,17 +1203,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124766669</v>
+        <v>123577092</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337924</v>
+        <v>337869</v>
       </c>
       <c r="R5" t="n">
-        <v>6426985</v>
+        <v>6427098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,22 +1092,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123577092</v>
+        <v>124766654</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57664</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,16 +1145,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R6" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,17 +1203,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123577092</v>
+        <v>124766669</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57664</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R5" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,17 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124766654</v>
+        <v>123577092</v>
       </c>
       <c r="B6" t="n">
-        <v>57664</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,16 +1150,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337924</v>
+        <v>337869</v>
       </c>
       <c r="R6" t="n">
-        <v>6426985</v>
+        <v>6427098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,22 +1208,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124766669</v>
+        <v>123577092</v>
       </c>
       <c r="B5" t="n">
-        <v>57664</v>
+        <v>57632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337924</v>
+        <v>337869</v>
       </c>
       <c r="R5" t="n">
-        <v>6426985</v>
+        <v>6427098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,22 +1092,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123577092</v>
+        <v>124766669</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57791</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,16 +1145,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R6" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,17 +1203,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123577092</v>
+        <v>124766654</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
+        <v>57791</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R5" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,17 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124766669</v>
+        <v>123577092</v>
       </c>
       <c r="B6" t="n">
-        <v>57791</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,16 +1150,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337924</v>
+        <v>337869</v>
       </c>
       <c r="R6" t="n">
-        <v>6426985</v>
+        <v>6427098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,22 +1208,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>123576440</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -774,31 +769,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123787951</v>
+        <v>123577092</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -826,17 +816,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jonsatorp, Vg</t>
+          <t>Hällebäckahult, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337931</v>
+        <v>337869</v>
       </c>
       <c r="R3" t="n">
-        <v>6426938</v>
+        <v>6427098</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,22 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack i träd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -905,16 +890,11 @@
         <v>123787899</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1018,27 +998,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124766669</v>
+        <v>123787951</v>
       </c>
       <c r="B5" t="n">
-        <v>57791</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1053,17 +1033,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällebäckahult, Vg</t>
+          <t>Jonsatorp, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337924</v>
+        <v>337931</v>
       </c>
       <c r="R5" t="n">
-        <v>6426985</v>
+        <v>6426938</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,22 +1067,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,22 +1097,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123577092</v>
+        <v>124766654</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,16 +1120,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1168,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337869</v>
+        <v>337924</v>
       </c>
       <c r="R6" t="n">
-        <v>6427098</v>
+        <v>6426985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,17 +1178,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack i träd</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,12 +1208,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 13380-2025 artfynd.xlsx
+++ b/artfynd/A 13380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123576440</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123577092</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123787899</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123787951</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,8 +1242,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124766654</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>